--- a/backend/data/financials_by_company/0033.HK.xlsx
+++ b/backend/data/financials_by_company/0033.HK.xlsx
@@ -3006,197 +3006,197 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Xiaobin  He', 'age': 63, 'title': 'Chief Economist', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 110000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yongxiang  Pan', 'age': 37, 'title': 'Executive Chairman', 'yearBorn': 1988, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hing Tok  Poon', 'age': 38, 'title': 'Executive Director', 'yearBorn': 1987, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kai Weng  Leong', 'age': 38, 'title': 'Company Secretary', 'yearBorn': 1987, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. Xiaobin  He', 'age': 63, 'title': 'Chief Economist', 'yearBorn': 1962, 'fiscalYear': 2024, 'totalPay': 110000, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yongxiang  Pan', 'age': 37, 'title': 'Executive Chairman', 'yearBorn': 1988, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Hing Tok  Poon', 'age': 38, 'title': 'Executive Director', 'yearBorn': 1987, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Kai Weng  Leong', 'age': 39, 'title': 'Company Secretary', 'yearBorn': 1986, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3319,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.174</v>
+        <v>-0.201</v>
       </c>
       <c r="AD2" t="n">
         <v>302800</v>
@@ -3373,7 +3373,7 @@
         <v>0.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.402025</v>
+        <v>0.400925</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>-28.473</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.48717946</v>
+        <v>-0.44444442</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BU2" t="n">
         <v>3.662501</v>
@@ -3567,148 +3567,148 @@
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
           <t>INTL GENIUS</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>International Genius Company</t>
+        </is>
+      </c>
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>finmb_38798295</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>1759219682</v>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1195435800000</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="inlineStr">
         <is>
           <t>0.395 - 0.415</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF2" t="n">
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
         <v>0.01000002</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DV2" t="n">
         <v>0.025641078</v>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>0.39 - 1.05</t>
         </is>
       </c>
-      <c r="DI2" t="n">
+      <c r="DX2" t="n">
         <v>-0.65</v>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DY2" t="n">
         <v>-0.61904764</v>
       </c>
-      <c r="DK2" t="n">
-        <v>-48.717945</v>
-      </c>
-      <c r="DL2" t="n">
+      <c r="DZ2" t="n">
+        <v>-44.444443</v>
+      </c>
+      <c r="EA2" t="n">
         <v>1740738281</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="EB2" t="n">
         <v>1740738281</v>
       </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
         <v>-0.03</v>
       </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.0020250082</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>-0.0050370204</v>
-      </c>
-      <c r="DT2" t="n">
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.0009250044999999999</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.002307176</v>
+      </c>
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="DV2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Amber Hill Financial Holdings Limited</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="DX2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1195435800000</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>International Genius Company</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>1759219682</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>finmb_38798295</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
       </c>
       <c r="EM2" t="inlineStr"/>
     </row>
